--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>6.78</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>4.35</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>3.8</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>3.79</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>3.45</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>3.39</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>3.03</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>2.92</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -499,9 +470,6 @@
       </c>
       <c r="B10">
         <v>2.32</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>6.78</v>
       </c>
+      <c r="C2">
+        <v>6.7</v>
+      </c>
+      <c r="D2">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="E2">
+        <v>1.194029850746259</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>4.35</v>
       </c>
+      <c r="C3">
+        <v>4.34</v>
+      </c>
+      <c r="D3">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E3">
+        <v>0.2304147465437723</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>3.8</v>
       </c>
+      <c r="C4">
+        <v>3.91</v>
+      </c>
+      <c r="D4">
+        <v>-0.1100000000000003</v>
+      </c>
+      <c r="E4">
+        <v>-2.813299232736577</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>3.79</v>
       </c>
+      <c r="C5">
+        <v>3.85</v>
+      </c>
+      <c r="D5">
+        <v>-0.06000000000000005</v>
+      </c>
+      <c r="E5">
+        <v>-1.558441558441559</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>3.45</v>
       </c>
+      <c r="C6">
+        <v>3.2</v>
+      </c>
+      <c r="D6">
+        <v>0.25</v>
+      </c>
+      <c r="E6">
+        <v>7.8125</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,35 +486,90 @@
       <c r="B7">
         <v>3.39</v>
       </c>
+      <c r="C7">
+        <v>3.35</v>
+      </c>
+      <c r="D7">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="E7">
+        <v>1.194029850746259</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B8">
-        <v>3.03</v>
+        <v>3.2</v>
+      </c>
+      <c r="C8">
+        <v>3.4</v>
+      </c>
+      <c r="D8">
+        <v>-0.1999999999999997</v>
+      </c>
+      <c r="E8">
+        <v>-5.88235294117646</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Tierra Amarilla</t>
         </is>
       </c>
       <c r="B9">
-        <v>2.92</v>
+        <v>3.03</v>
+      </c>
+      <c r="C9">
+        <v>3.37</v>
+      </c>
+      <c r="D9">
+        <v>-0.3400000000000003</v>
+      </c>
+      <c r="E9">
+        <v>-10.08902077151336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2.92</v>
+      </c>
+      <c r="C10">
+        <v>3.25</v>
+      </c>
+      <c r="D10">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="E10">
+        <v>-10.15384615384616</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Diego de Almagro</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>2.32</v>
+      </c>
+      <c r="C11">
+        <v>2.07</v>
+      </c>
+      <c r="D11">
+        <v>0.25</v>
+      </c>
+      <c r="E11">
+        <v>12.07729468599035</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_atacama.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,11 +588,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,28 +595,19 @@
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="B2">
-        <v>6.78</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caldera</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>3.79</v>
+          <t>Freirina</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chañaral</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
+          <t>Huasco</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -630,48 +616,33 @@
           <t>Copiapó</t>
         </is>
       </c>
-      <c r="B5">
-        <v>2.92</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2.32</v>
+          <t>Caldera</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Freirina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.35</v>
+          <t>Chañaral</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Huasco</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>3.39</v>
+          <t>Tierra Amarilla</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>3.03</v>
+          <t>Diego de Almagro</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -679,9 +650,6 @@
         <is>
           <t>Vallenar</t>
         </is>
-      </c>
-      <c r="B10">
-        <v>3.8</v>
       </c>
     </row>
   </sheetData>
